--- a/exports/trend_1d/NTPC_full_report.xlsx
+++ b/exports/trend_1d/NTPC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.91</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42082</v>
+        <v>42083</v>
       </c>
       <c r="H2" t="n">
-        <v>128.96</v>
+        <v>121.25</v>
       </c>
       <c r="I2" t="n">
         <v>122.5718226803746</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K2" t="n">
-        <v>11.18</v>
+        <v>4.53</v>
       </c>
       <c r="L2" t="n">
         <v>1.75</v>
       </c>
       <c r="M2" t="n">
-        <v>1.54</v>
+        <v>7.08</v>
       </c>
       <c r="N2" t="n">
-        <v>4.01</v>
+        <v>5.98</v>
       </c>
       <c r="O2" t="n">
         <v>1.05</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.19</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42261</v>
+        <v>42262</v>
       </c>
       <c r="H3" t="n">
-        <v>104.92</v>
+        <v>105.71</v>
       </c>
       <c r="I3" t="n">
         <v>105.6309994027626</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K3" t="n">
-        <v>13.47</v>
+        <v>12.82</v>
       </c>
       <c r="L3" t="n">
         <v>9.960000000000001</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>7</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.44</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H4" t="n">
-        <v>119.33</v>
+        <v>113.71</v>
       </c>
       <c r="I4" t="n">
         <v>114.5462768444597</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K4" t="n">
-        <v>12.88</v>
+        <v>7.57</v>
       </c>
       <c r="L4" t="n">
         <v>6.19</v>
@@ -669,7 +716,7 @@
         <v>1.64</v>
       </c>
       <c r="N4" t="n">
-        <v>4.62</v>
+        <v>4.71</v>
       </c>
       <c r="O4" t="n">
         <v>0.75</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.12</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42468</v>
+        <v>42471</v>
       </c>
       <c r="H5" t="n">
-        <v>109.63</v>
+        <v>112.17</v>
       </c>
       <c r="I5" t="n">
         <v>109.9300665386088</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K5" t="n">
-        <v>3.59</v>
+        <v>1.35</v>
       </c>
       <c r="L5" t="n">
         <v>7.51</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42622</v>
+        <v>42625</v>
       </c>
       <c r="H6" t="n">
-        <v>132.33</v>
+        <v>127.38</v>
       </c>
       <c r="I6" t="n">
         <v>131.2333031985141</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K6" t="n">
-        <v>17.97</v>
+        <v>13.56</v>
       </c>
       <c r="L6" t="n">
         <v>2.49</v>
@@ -783,7 +854,7 @@
         <v>9.99</v>
       </c>
       <c r="N6" t="n">
-        <v>2.84</v>
+        <v>3.74</v>
       </c>
       <c r="O6" t="n">
         <v>2.32</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42671</v>
+        <v>42675</v>
       </c>
       <c r="H7" t="n">
-        <v>126.88</v>
+        <v>129.17</v>
       </c>
       <c r="I7" t="n">
         <v>128.9838067524594</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K7" t="n">
-        <v>0.39</v>
+        <v>-1.41</v>
       </c>
       <c r="L7" t="n">
         <v>3.49</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.08</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42793</v>
+        <v>42794</v>
       </c>
       <c r="H8" t="n">
-        <v>137.83</v>
+        <v>135.79</v>
       </c>
       <c r="I8" t="n">
         <v>136.6054056405382</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K8" t="n">
-        <v>6.7</v>
+        <v>5.13</v>
       </c>
       <c r="L8" t="n">
         <v>6.07</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.56</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42830</v>
+        <v>42831</v>
       </c>
       <c r="H9" t="n">
-        <v>138.75</v>
+        <v>139.75</v>
       </c>
       <c r="I9" t="n">
         <v>139.6482536935218</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.18</v>
+        <v>-2.92</v>
       </c>
       <c r="L9" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="M9" t="n">
         <v>2.13</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>6.04</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42872</v>
+        <v>42873</v>
       </c>
       <c r="H10" t="n">
-        <v>132.42</v>
+        <v>131.5</v>
       </c>
       <c r="I10" t="n">
         <v>132.1679604423463</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.25</v>
+        <v>-5.9</v>
       </c>
       <c r="L10" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="M10" t="n">
-        <v>0.42</v>
+        <v>0.57</v>
       </c>
       <c r="N10" t="n">
         <v>3.25</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>5.33</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42927</v>
+        <v>42928</v>
       </c>
       <c r="H11" t="n">
-        <v>136.08</v>
+        <v>136.71</v>
       </c>
       <c r="I11" t="n">
         <v>136.4341363906513</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.48</v>
+        <v>-3.96</v>
       </c>
       <c r="L11" t="n">
         <v>7.73</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.78</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43111</v>
+        <v>43112</v>
       </c>
       <c r="H12" t="n">
-        <v>144.58</v>
+        <v>143.75</v>
       </c>
       <c r="I12" t="n">
         <v>144.1346238009145</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K12" t="n">
-        <v>5.76</v>
+        <v>5.15</v>
       </c>
       <c r="L12" t="n">
         <v>1.38</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>4.8</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43168</v>
+        <v>43171</v>
       </c>
       <c r="H13" t="n">
-        <v>137</v>
+        <v>142.63</v>
       </c>
       <c r="I13" t="n">
         <v>142.0910726806909</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K13" t="n">
-        <v>4.7</v>
+        <v>0.78</v>
       </c>
       <c r="L13" t="n">
         <v>2.18</v>
@@ -1182,7 +1337,7 @@
         <v>0.65</v>
       </c>
       <c r="N13" t="n">
-        <v>1.74</v>
+        <v>4.11</v>
       </c>
       <c r="O13" t="n">
         <v>-0.57</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.99</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43230</v>
+        <v>43231</v>
       </c>
       <c r="H14" t="n">
-        <v>140.42</v>
+        <v>139.54</v>
       </c>
       <c r="I14" t="n">
         <v>140.4159597659737</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.55</v>
+        <v>-2.17</v>
       </c>
       <c r="L14" t="n">
         <v>4.38</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.57</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43333</v>
+        <v>43335</v>
       </c>
       <c r="H15" t="n">
-        <v>134.04</v>
+        <v>136.96</v>
       </c>
       <c r="I15" t="n">
         <v>135.1954916209793</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K15" t="n">
-        <v>3.94</v>
+        <v>1.85</v>
       </c>
       <c r="L15" t="n">
         <v>3.88</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>7.02</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43398</v>
+        <v>43399</v>
       </c>
       <c r="H16" t="n">
-        <v>135.25</v>
+        <v>132.75</v>
       </c>
       <c r="I16" t="n">
         <v>134.0225929140554</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.25</v>
+        <v>-3.07</v>
       </c>
       <c r="L16" t="n">
-        <v>4.29</v>
+        <v>5.81</v>
       </c>
       <c r="M16" t="n">
-        <v>1.43</v>
+        <v>2.06</v>
       </c>
       <c r="N16" t="n">
         <v>2.34</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43452</v>
+        <v>43453</v>
       </c>
       <c r="H17" t="n">
-        <v>123.08</v>
+        <v>124.83</v>
       </c>
       <c r="I17" t="n">
         <v>124.2775290815188</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K17" t="n">
-        <v>7.28</v>
+        <v>5.97</v>
       </c>
       <c r="L17" t="n">
         <v>1.1</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43497</v>
+        <v>43500</v>
       </c>
       <c r="H18" t="n">
-        <v>116.79</v>
+        <v>114.38</v>
       </c>
       <c r="I18" t="n">
         <v>114.7160790544329</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.44</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L18" t="n">
         <v>8.77</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>7.39</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43523</v>
+        <v>43524</v>
       </c>
       <c r="H19" t="n">
-        <v>115.63</v>
+        <v>117.71</v>
       </c>
       <c r="I19" t="n">
         <v>117.4557821469397</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.09</v>
+        <v>-2.91</v>
       </c>
       <c r="L19" t="n">
         <v>4.15</v>
       </c>
       <c r="M19" t="n">
-        <v>0.57</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
         <v>3.8</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>10.2</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43593</v>
+        <v>43594</v>
       </c>
       <c r="H20" t="n">
-        <v>130.8</v>
+        <v>127.7</v>
       </c>
       <c r="I20" t="n">
         <v>127.8452623454584</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K20" t="n">
-        <v>11.12</v>
+        <v>8.49</v>
       </c>
       <c r="L20" t="n">
         <v>2.09</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.84</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43614</v>
+        <v>43615</v>
       </c>
       <c r="H21" t="n">
-        <v>130.9</v>
+        <v>135.1</v>
       </c>
       <c r="I21" t="n">
         <v>134.0128529804817</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.51</v>
+        <v>-5.79</v>
       </c>
       <c r="L21" t="n">
         <v>6.97</v>
@@ -1638,7 +1889,7 @@
         <v>2.52</v>
       </c>
       <c r="N21" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="O21" t="n">
         <v>-2.37</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H22" t="n">
-        <v>136.5</v>
+        <v>129.6</v>
       </c>
       <c r="I22" t="n">
         <v>134.7272529570441</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K22" t="n">
-        <v>1.04</v>
+        <v>-4.07</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>4.85</v>
       </c>
       <c r="M22" t="n">
         <v>0.45</v>
       </c>
       <c r="N22" t="n">
-        <v>4.84</v>
+        <v>5.05</v>
       </c>
       <c r="O22" t="n">
         <v>3.21</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>11.33</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43713</v>
+        <v>43714</v>
       </c>
       <c r="H23" t="n">
-        <v>123.45</v>
+        <v>127</v>
       </c>
       <c r="I23" t="n">
         <v>126.6599027470051</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K23" t="n">
-        <v>4.75</v>
+        <v>2.01</v>
       </c>
       <c r="L23" t="n">
         <v>5.4</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>12.84</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43801</v>
+        <v>43802</v>
       </c>
       <c r="H24" t="n">
-        <v>115.3</v>
+        <v>114.55</v>
       </c>
       <c r="I24" t="n">
         <v>114.6958252366868</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K24" t="n">
-        <v>-9.210000000000001</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L24" t="n">
         <v>10.2</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>5.65</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43829</v>
+        <v>43830</v>
       </c>
       <c r="H25" t="n">
-        <v>116.55</v>
+        <v>119.05</v>
       </c>
       <c r="I25" t="n">
         <v>117.5856817045101</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.75</v>
+        <v>-3.93</v>
       </c>
       <c r="L25" t="n">
-        <v>3.27</v>
+        <v>4.5</v>
       </c>
       <c r="M25" t="n">
         <v>0.53</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>6.29</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43851</v>
+        <v>43852</v>
       </c>
       <c r="H26" t="n">
-        <v>117.15</v>
+        <v>112.15</v>
       </c>
       <c r="I26" t="n">
         <v>116.3545418892907</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.6</v>
+        <v>-5.8</v>
       </c>
       <c r="L26" t="n">
-        <v>2.27</v>
+        <v>6.34</v>
       </c>
       <c r="M26" t="n">
-        <v>0.71</v>
+        <v>1.88</v>
       </c>
       <c r="N26" t="n">
-        <v>2.43</v>
+        <v>4.27</v>
       </c>
       <c r="O26" t="n">
         <v>2.15</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43938</v>
+        <v>43941</v>
       </c>
       <c r="H27" t="n">
-        <v>95.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>97.35076362883704</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K27" t="n">
-        <v>14.85</v>
+        <v>11.81</v>
       </c>
       <c r="L27" t="n">
         <v>6.02</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>19.88</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44025</v>
+        <v>44026</v>
       </c>
       <c r="H28" t="n">
-        <v>89.90000000000001</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="I28" t="n">
         <v>88.74050639785706</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K28" t="n">
-        <v>-9.1</v>
+        <v>-11.38</v>
       </c>
       <c r="L28" t="n">
         <v>13.4</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>10.57</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44057</v>
+        <v>44060</v>
       </c>
       <c r="H29" t="n">
-        <v>88.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="I29" t="n">
         <v>92.04966477154855</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.86</v>
+        <v>-8.73</v>
       </c>
       <c r="L29" t="n">
-        <v>5.65</v>
+        <v>10.1</v>
       </c>
       <c r="M29" t="n">
         <v>1.17</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>7.81</v>
       </c>
       <c r="O29" t="n">
         <v>-2.5</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>11.22</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44077</v>
+        <v>44078</v>
       </c>
       <c r="H30" t="n">
-        <v>97.7</v>
+        <v>94.7</v>
       </c>
       <c r="I30" t="n">
         <v>94.76122880855092</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K30" t="n">
-        <v>2.52</v>
+        <v>-0.63</v>
       </c>
       <c r="L30" t="n">
         <v>6.19</v>
       </c>
       <c r="M30" t="n">
-        <v>0.05</v>
+        <v>1.69</v>
       </c>
       <c r="N30" t="n">
         <v>5.07</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>12.67</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44130</v>
+        <v>44131</v>
       </c>
       <c r="H31" t="n">
-        <v>85.95</v>
+        <v>89.45</v>
       </c>
       <c r="I31" t="n">
         <v>86.6324099386152</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K31" t="n">
-        <v>9.24</v>
+        <v>5.54</v>
       </c>
       <c r="L31" t="n">
         <v>2.9</v>
       </c>
       <c r="M31" t="n">
-        <v>1.59</v>
+        <v>3.32</v>
       </c>
       <c r="N31" t="n">
-        <v>3.18</v>
+        <v>4.07</v>
       </c>
       <c r="O31" t="n">
         <v>-3.07</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.52</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44216</v>
+        <v>44217</v>
       </c>
       <c r="H32" t="n">
-        <v>98.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I32" t="n">
         <v>96.86030476707299</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K32" t="n">
-        <v>9.890000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="L32" t="n">
         <v>7.15</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,25 +2696,25 @@
         <v>10.27</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44231</v>
+        <v>44232</v>
       </c>
       <c r="H33" t="n">
-        <v>99.05</v>
+        <v>99.5</v>
       </c>
       <c r="I33" t="n">
         <v>99.26454053832663</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.07</v>
+        <v>-3.54</v>
       </c>
       <c r="L33" t="n">
-        <v>4.27</v>
+        <v>6.14</v>
       </c>
       <c r="M33" t="n">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="N33" t="n">
         <v>3.43</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.23</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44295</v>
+        <v>44298</v>
       </c>
       <c r="H34" t="n">
-        <v>102.8</v>
+        <v>99.05</v>
       </c>
       <c r="I34" t="n">
         <v>101.3243821067277</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K34" t="n">
-        <v>3.32</v>
+        <v>-0.45</v>
       </c>
       <c r="L34" t="n">
         <v>4.72</v>
@@ -2379,7 +2786,7 @@
         <v>3.32</v>
       </c>
       <c r="N34" t="n">
-        <v>2.83</v>
+        <v>3.65</v>
       </c>
       <c r="O34" t="n">
         <v>0.45</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>10.98</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44326</v>
+        <v>44327</v>
       </c>
       <c r="H35" t="n">
-        <v>107.7</v>
+        <v>112.7</v>
       </c>
       <c r="I35" t="n">
         <v>107.8948062955198</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K35" t="n">
-        <v>-8.73</v>
+        <v>-13.78</v>
       </c>
       <c r="L35" t="n">
-        <v>9.039999999999999</v>
+        <v>14.49</v>
       </c>
       <c r="M35" t="n">
         <v>1.37</v>
       </c>
       <c r="N35" t="n">
-        <v>3.64</v>
+        <v>4.64</v>
       </c>
       <c r="O35" t="n">
         <v>-3.65</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>11.12</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44428</v>
+        <v>44431</v>
       </c>
       <c r="H36" t="n">
-        <v>114.15</v>
+        <v>113.4</v>
       </c>
       <c r="I36" t="n">
         <v>113.4067710123915</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K36" t="n">
-        <v>1.29</v>
+        <v>0.62</v>
       </c>
       <c r="L36" t="n">
         <v>5.32</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>7.73</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44453</v>
+        <v>44454</v>
       </c>
       <c r="H37" t="n">
-        <v>115.9</v>
+        <v>124.2</v>
       </c>
       <c r="I37" t="n">
         <v>120.2698839647843</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.2</v>
+        <v>-9.52</v>
       </c>
       <c r="L37" t="n">
-        <v>3.97</v>
+        <v>10.1</v>
       </c>
       <c r="M37" t="n">
         <v>1.18</v>
       </c>
       <c r="N37" t="n">
-        <v>1.37</v>
+        <v>7.16</v>
       </c>
       <c r="O37" t="n">
         <v>-0.66</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.56</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44496</v>
+        <v>44497</v>
       </c>
       <c r="H38" t="n">
-        <v>141.3</v>
+        <v>137.35</v>
       </c>
       <c r="I38" t="n">
         <v>137.7522954861307</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K38" t="n">
-        <v>13.77</v>
+        <v>10.59</v>
       </c>
       <c r="L38" t="n">
         <v>6.6</v>
@@ -2607,7 +3062,7 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="O38" t="n">
         <v>7.16</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.12</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44564</v>
+        <v>44565</v>
       </c>
       <c r="H39" t="n">
-        <v>126</v>
+        <v>132.9</v>
       </c>
       <c r="I39" t="n">
         <v>131.3318962314234</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K39" t="n">
-        <v>8.26</v>
+        <v>3.24</v>
       </c>
       <c r="L39" t="n">
         <v>3.28</v>
@@ -2664,7 +3131,7 @@
         <v>2.16</v>
       </c>
       <c r="N39" t="n">
-        <v>3.05</v>
+        <v>5.48</v>
       </c>
       <c r="O39" t="n">
         <v>-2.8</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.43</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44614</v>
+        <v>44615</v>
       </c>
       <c r="H40" t="n">
-        <v>132.1</v>
+        <v>130.2</v>
       </c>
       <c r="I40" t="n">
         <v>130.6780579869231</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.6</v>
+        <v>-2.03</v>
       </c>
       <c r="L40" t="n">
         <v>4.63</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>9.19</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44651</v>
+        <v>44652</v>
       </c>
       <c r="H41" t="n">
-        <v>135</v>
+        <v>142.95</v>
       </c>
       <c r="I41" t="n">
         <v>137.7561338784131</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.69</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>4.57</v>
+        <v>10.18</v>
       </c>
       <c r="M41" t="n">
-        <v>1.06</v>
+        <v>2.22</v>
       </c>
       <c r="N41" t="n">
-        <v>4.78</v>
+        <v>5.89</v>
       </c>
       <c r="O41" t="n">
         <v>-1.44</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.26</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44692</v>
+        <v>44693</v>
       </c>
       <c r="H42" t="n">
-        <v>152.55</v>
+        <v>148.55</v>
       </c>
       <c r="I42" t="n">
         <v>149.1527921594329</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K42" t="n">
-        <v>6.72</v>
+        <v>3.92</v>
       </c>
       <c r="L42" t="n">
         <v>4.3</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>11.09</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44760</v>
+        <v>44761</v>
       </c>
       <c r="H43" t="n">
-        <v>149.8</v>
+        <v>150.75</v>
       </c>
       <c r="I43" t="n">
         <v>150.2102994739322</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.84</v>
+        <v>-1.48</v>
       </c>
       <c r="L43" t="n">
         <v>7.84</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.85</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H44" t="n">
-        <v>163.95</v>
+        <v>158.6</v>
       </c>
       <c r="I44" t="n">
         <v>161.9764788446028</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K44" t="n">
-        <v>8.76</v>
+        <v>5.21</v>
       </c>
       <c r="L44" t="n">
         <v>2.26</v>
@@ -2949,7 +3476,7 @@
         <v>1.57</v>
       </c>
       <c r="N44" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="O44" t="n">
         <v>0.63</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44859</v>
+        <v>44861</v>
       </c>
       <c r="H45" t="n">
-        <v>169.35</v>
+        <v>170.65</v>
       </c>
       <c r="I45" t="n">
         <v>170.1927154340258</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.78</v>
+        <v>-7.6</v>
       </c>
       <c r="L45" t="n">
-        <v>7</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M45" t="n">
         <v>1.15</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>7.7</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44882</v>
+        <v>44883</v>
       </c>
       <c r="H46" t="n">
-        <v>168.3</v>
+        <v>165.85</v>
       </c>
       <c r="I46" t="n">
         <v>167.7317069707908</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.38</v>
+        <v>-2.81</v>
       </c>
       <c r="L46" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="M46" t="n">
         <v>2.38</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>7.88</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44988</v>
+        <v>44991</v>
       </c>
       <c r="H47" t="n">
-        <v>172.6</v>
+        <v>176.8</v>
       </c>
       <c r="I47" t="n">
         <v>174.0174245991558</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.07</v>
+        <v>-6.6</v>
       </c>
       <c r="L47" t="n">
-        <v>6.12</v>
+        <v>7.02</v>
       </c>
       <c r="M47" t="n">
         <v>0.84</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>6.7</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45029</v>
+        <v>45033</v>
       </c>
       <c r="H48" t="n">
-        <v>173.05</v>
+        <v>169.6</v>
       </c>
       <c r="I48" t="n">
         <v>170.5191215832682</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.12</v>
+        <v>-4.07</v>
       </c>
       <c r="L48" t="n">
-        <v>3.56</v>
+        <v>4.27</v>
       </c>
       <c r="M48" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>1.56</v>
+        <v>1.99</v>
       </c>
       <c r="O48" t="n">
         <v>2.43</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>6.94</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45056</v>
+        <v>45057</v>
       </c>
       <c r="H49" t="n">
-        <v>177.05</v>
+        <v>179.55</v>
       </c>
       <c r="I49" t="n">
         <v>177.7515956004659</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.39</v>
+        <v>-5.87</v>
       </c>
       <c r="L49" t="n">
-        <v>5.34</v>
+        <v>6.13</v>
       </c>
       <c r="M49" t="n">
         <v>0.5600000000000001</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.63</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H50" t="n">
-        <v>344.75</v>
+        <v>322.5</v>
       </c>
       <c r="I50" t="n">
         <v>330.7975348483769</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K50" t="n">
-        <v>92.01000000000001</v>
+        <v>79.62</v>
       </c>
       <c r="L50" t="n">
         <v>4.29</v>
@@ -3291,7 +3890,7 @@
         <v>1.15</v>
       </c>
       <c r="N50" t="n">
-        <v>3.88</v>
+        <v>6.45</v>
       </c>
       <c r="O50" t="n">
         <v>1.41</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>211</v>
+        <v>212</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>11</v>
+      </c>
+      <c r="U50" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>12.28</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="H51" t="n">
-        <v>342.35</v>
+        <v>344.8</v>
       </c>
       <c r="I51" t="n">
         <v>343.9238041917325</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.16</v>
+        <v>-6.91</v>
       </c>
       <c r="L51" t="n">
-        <v>6.82</v>
+        <v>7.16</v>
       </c>
       <c r="M51" t="n">
         <v>1.15</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H52" t="n">
-        <v>391.8</v>
+        <v>331.25</v>
       </c>
       <c r="I52" t="n">
         <v>348.9534027847826</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K52" t="n">
-        <v>13.63</v>
+        <v>-3.93</v>
       </c>
       <c r="L52" t="n">
-        <v>1.17</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M52" t="n">
         <v>2.29</v>
       </c>
       <c r="N52" t="n">
-        <v>2.64</v>
+        <v>15.45</v>
       </c>
       <c r="O52" t="n">
         <v>0.72</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>22.94</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45496</v>
+        <v>45497</v>
       </c>
       <c r="H53" t="n">
-        <v>382.45</v>
+        <v>392.6</v>
       </c>
       <c r="I53" t="n">
         <v>385.7474937443261</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K53" t="n">
-        <v>-15.46</v>
+        <v>-18.52</v>
       </c>
       <c r="L53" t="n">
-        <v>18.31</v>
+        <v>19.25</v>
       </c>
       <c r="M53" t="n">
         <v>2.64</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.32</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45587</v>
+        <v>45588</v>
       </c>
       <c r="H54" t="n">
-        <v>415.75</v>
+        <v>408.3</v>
       </c>
       <c r="I54" t="n">
         <v>413.6056022642987</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K54" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="L54" t="n">
         <v>2.78</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.73</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45674</v>
+        <v>45677</v>
       </c>
       <c r="H55" t="n">
-        <v>326.15</v>
+        <v>336.05</v>
       </c>
       <c r="I55" t="n">
         <v>330.7348627659612</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K55" t="n">
-        <v>20.12</v>
+        <v>17.7</v>
       </c>
       <c r="L55" t="n">
         <v>1.75</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>10.12</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H56" t="n">
-        <v>306.7</v>
+        <v>300.35</v>
       </c>
       <c r="I56" t="n">
         <v>302.0337218853275</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K56" t="n">
-        <v>-8.73</v>
+        <v>-10.62</v>
       </c>
       <c r="L56" t="n">
-        <v>10.73</v>
+        <v>11.22</v>
       </c>
       <c r="M56" t="n">
         <v>2.39</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45707</v>
+        <v>45708</v>
       </c>
       <c r="H57" t="n">
-        <v>314.8</v>
+        <v>325.15</v>
       </c>
       <c r="I57" t="n">
         <v>325.1477926613233</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.81</v>
+        <v>-8.26</v>
       </c>
       <c r="L57" t="n">
-        <v>5.33</v>
+        <v>8.92</v>
       </c>
       <c r="M57" t="n">
         <v>0.05</v>
       </c>
       <c r="N57" t="n">
-        <v>2.93</v>
+        <v>3.29</v>
       </c>
       <c r="O57" t="n">
         <v>-2.07</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>10.91</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45784</v>
+        <v>45785</v>
       </c>
       <c r="H58" t="n">
-        <v>342.05</v>
+        <v>340</v>
       </c>
       <c r="I58" t="n">
         <v>340.6942067843901</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K58" t="n">
-        <v>5.2</v>
+        <v>4.57</v>
       </c>
       <c r="L58" t="n">
         <v>5.72</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.7</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="H59" t="n">
-        <v>339.2</v>
+        <v>343</v>
       </c>
       <c r="I59" t="n">
         <v>341.6777762759309</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K59" t="n">
-        <v>0.24</v>
+        <v>-0.88</v>
       </c>
       <c r="L59" t="n">
         <v>3.29</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>5</v>
+      </c>
+      <c r="U59" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>4.6</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H60" t="n">
-        <v>335.2</v>
+        <v>330.6</v>
       </c>
       <c r="I60" t="n">
         <v>331.403103906962</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.27</v>
+        <v>-3.62</v>
       </c>
       <c r="L60" t="n">
-        <v>3.44</v>
+        <v>3.88</v>
       </c>
       <c r="M60" t="n">
         <v>0.52</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.87</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46022</v>
+        <v>46023</v>
       </c>
       <c r="H61" t="n">
-        <v>329.55</v>
+        <v>336.3</v>
       </c>
       <c r="I61" t="n">
         <v>331.4925080320311</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K61" t="n">
-        <v>0.32</v>
+        <v>-1.72</v>
       </c>
       <c r="L61" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="M61" t="n">
         <v>0.44</v>
       </c>
       <c r="N61" t="n">
-        <v>1.43</v>
+        <v>2.05</v>
       </c>
       <c r="O61" t="n">
         <v>-1.37</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>4.79</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H62" t="n">
-        <v>364.65</v>
+        <v>359.65</v>
       </c>
       <c r="I62" t="n">
         <v>362.9940500345576</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K62" t="n">
-        <v>8.43</v>
+        <v>6.94</v>
       </c>
       <c r="L62" t="n">
         <v>1.99</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>7.69</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H63" t="n">
-        <v>386.25</v>
+        <v>392.6</v>
       </c>
       <c r="I63" t="n">
         <v>387.2961658086866</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K63" t="n">
-        <v>-7.4</v>
+        <v>-9.16</v>
       </c>
       <c r="L63" t="n">
-        <v>7.88</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M63" t="n">
         <v>1.26</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>8.27</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="H64" t="n">
-        <v>386.9</v>
+        <v>378.7</v>
       </c>
       <c r="I64" t="n">
         <v>381.7893772780631</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.45</v>
+        <v>-3.54</v>
       </c>
       <c r="L64" t="n">
-        <v>2.19</v>
+        <v>4.1</v>
       </c>
       <c r="M64" t="n">
         <v>0.85</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,14 @@
       <c r="Q65" t="n">
         <v>104</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9107,7 +9894,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.40000000000001</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -9117,7 +9904,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -9127,7 +9914,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8">
@@ -9137,7 +9924,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9147,7 +9934,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.5</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="10">
@@ -9157,7 +9944,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115.4</v>
+        <v>116.8</v>
       </c>
     </row>
     <row r="11">
@@ -9167,7 +9954,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -9177,7 +9964,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -9187,7 +9974,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.8</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="14">
@@ -9197,7 +9984,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.16</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="15">
@@ -9207,7 +9994,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.85</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="16">
@@ -9217,7 +10004,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.38</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="17">
@@ -9227,7 +10014,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>92.01000000000001</v>
+        <v>79.62</v>
       </c>
     </row>
     <row r="18">
@@ -9237,7 +10024,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.8</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="19">
@@ -9247,7 +10034,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.09</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="20">
@@ -9257,7 +10044,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.38</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="21">
@@ -9267,7 +10054,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.31</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="22">
@@ -9277,7 +10064,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -9287,7 +10074,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -9297,7 +10084,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="25">
@@ -9317,7 +10104,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.23</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="27">
@@ -9327,7 +10114,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.02</v>
+        <v>15.45</v>
       </c>
     </row>
     <row r="28">
@@ -9337,7 +10124,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
